--- a/multimodal/多模态在线推理_HOST侧软件优化需求列表.xlsx
+++ b/multimodal/多模态在线推理_HOST侧软件优化需求列表.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="Re62e6eef8b9849c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="软件优化需求" sheetId="2" r:id="Re6ebe70e96934def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径与来源" sheetId="3" r:id="R6fbf9a33a6ca40b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="评审总览" sheetId="1" r:id="R771ad95350a048a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="软件优化需求" sheetId="2" r:id="R25c0ca04dc874943"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径与来源" sheetId="3" r:id="Rd5d73ff9feb84807"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -206,7 +206,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="61">
+  <x:cellXfs count="62">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -351,6 +351,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -468,7 +471,7 @@
         <x:color rgb="FF274E13"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
@@ -478,7 +481,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -488,7 +491,7 @@
         <x:color rgb="FF134F5C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAF7"/>
         </x:patternFill>
       </x:fill>
@@ -498,7 +501,7 @@
         <x:color rgb="FF3F3F3F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -655,7 +658,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R966070aa94324784"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4b61dc7a08dc49bf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -958,7 +961,7 @@
       </x:c>
       <x:c r="B5" s="16" t="n">
         <x:f>COUNTIF('软件优化需求'!$B$2:$B$36,$A$9)</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="13"/>
       <x:c r="D5" s="7"/>
@@ -973,7 +976,7 @@
       </x:c>
       <x:c r="B6" s="16" t="n">
         <x:f>COUNTIF('软件优化需求'!$B$2:$B$36,$A$10)</x:f>
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="13"/>
       <x:c r="D6" s="7"/>
@@ -1012,7 +1015,7 @@
       </x:c>
       <x:c r="B9" s="16" t="n">
         <x:f>COUNTIF('软件优化需求'!$B$2:$B$36,A9)</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="13"/>
       <x:c r="D9" s="13"/>
@@ -1027,7 +1030,7 @@
       </x:c>
       <x:c r="B10" s="16" t="n">
         <x:f>COUNTIF('软件优化需求'!$B$2:$B$36,A10)</x:f>
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="13"/>
       <x:c r="D10" s="13"/>
@@ -1057,7 +1060,7 @@
     <x:mergeCell ref="D3:H7"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bcde15ee2054b34"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40b19db9b8e14ddb"/>
 </x:worksheet>
 </file>
 
@@ -1071,7 +1074,7 @@
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="44" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="64" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="42" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
@@ -1081,10 +1084,10 @@
     <x:col min="14" max="14" width="46" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="40" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="22" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="58" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="62" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
+    <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="21" t="str">
         <x:v>需求ID</x:v>
       </x:c>
@@ -1103,7 +1106,7 @@
       <x:c r="F1" s="21" t="str">
         <x:v>当前核心瓶颈</x:v>
       </x:c>
-      <x:c r="G1" s="21" t="str">
+      <x:c r="G1" s="61" t="str">
         <x:v>软件优化需求</x:v>
       </x:c>
       <x:c r="H1" s="21" t="str">
@@ -1137,7 +1140,7 @@
         <x:v>主要真实负载库/执行层</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="78" customHeight="1">
+    <x:row r="2" ht="112" customHeight="1">
       <x:c r="A2" s="31" t="str">
         <x:v>SW-001</x:v>
       </x:c>
@@ -1157,7 +1160,7 @@
         <x:v>软解码、随机 seek、重复 demux 使 CPU 满载并造成 GPU 等待</x:v>
       </x:c>
       <x:c r="G2" s="32" t="str">
-        <x:v>提供一次顺序解码覆盖多个目标帧的抽帧 API；复用 demux/decoder；暴露实际解码帧数与 seek 次数</x:v>
+        <x:v>① 建立鲲鹏AArch64专用构建与基准，确认FFmpeg汇编/NEON路径生效，并按实际CPU提供NEON基线与可选SVE/SVE2多版本派发；② 顺序解码一次覆盖多个目标帧，复用demux/decoder/packet/frame；③ 融合抽帧、缩放、色彩和layout转换，直接写入下游buffer；④ 按NUMA与GPU拓扑配置codec线程、队列和内存归属，减少跨核迁移与重复拷贝。</x:v>
       </x:c>
       <x:c r="H2" s="32" t="str">
         <x:v>可复用视频抽帧组件、codec/GOP 基准、逐阶段打点</x:v>
@@ -1190,7 +1193,7 @@
         <x:v>主负载：libavcodec具体codec实现、libavformat demux、libswscale/libswresample及libc memcpy；CLI/Python绑定通常仅负责调度。</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="78" customHeight="1">
+    <x:row r="3" ht="112" customHeight="1">
       <x:c r="A3" s="34" t="str">
         <x:v>SW-002</x:v>
       </x:c>
@@ -1210,7 +1213,7 @@
         <x:v>JPEG 解码、颜色转换及多次 buffer 复制随总像素线性放大</x:v>
       </x:c>
       <x:c r="G3" s="35" t="str">
-        <x:v>直接输出目标 RGB/BGR 格式；复用 buffer；批量解码；建立 progressive JPEG 与 EXIF/ICC 兼容 fast path</x:v>
+        <x:v>① 鲲鹏平台统一使用启用AArch64 NEON SIMD的libjpeg-turbo构建，并校验运行时未退回标量路径；② 解码直接输出目标RGB/BGR/灰度格式，合并upsample、颜色转换和下游预处理；③ 建立批量/多图接口与可复用buffer池，降低小图调用和分配开销；④ 对自研颜色/layout融合模块在支持机型上评估SVE2实现，同时保持NEON与通用C回退。</x:v>
       </x:c>
       <x:c r="H3" s="35" t="str">
         <x:v>统一 JPEG codec 封装、图像语料基准、兼容性 golden</x:v>
@@ -1243,7 +1246,7 @@
         <x:v>主负载：libjpeg-turbo的IDCT、熵解码、颜色转换与SIMD内核；上层TurboJPEG API自身占比通常很低。</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="78" customHeight="1">
+    <x:row r="4" ht="112" customHeight="1">
       <x:c r="A4" s="34" t="str">
         <x:v>SW-003</x:v>
       </x:c>
@@ -1263,7 +1266,7 @@
         <x:v>PIL Image→NumPy→Tensor 多阶段对象和拷贝；高并发下对象分配明显</x:v>
       </x:c>
       <x:c r="G4" s="35" t="str">
-        <x:v>缩小 Pillow 责任边界；集中 EXIF/ICC/格式兼容；向下游暴露少拷贝 buffer；禁止重复 convert/resize</x:v>
+        <x:v>① 将Pillow限定为格式兼容、EXIF/ICC和控制面入口，批量像素处理下沉到libjpeg-turbo、OpenCV或torchvision原生路径；② 提供PIL→buffer/Tensor少拷贝接口，消除重复convert和Python对象构造；③ 发布鲲鹏AArch64 wheel并确保依赖的jpeg/zlib/webp/lcms库启用NEON优化；④ 按格式和输入类型建立fast path与兼容回退，避免在Python循环中逐图处理。</x:v>
       </x:c>
       <x:c r="H4" s="35" t="str">
         <x:v>Pillow 使用规范、兼容层、拷贝审计工具</x:v>
@@ -1296,7 +1299,7 @@
         <x:v>主负载：Pillow _imaging C扩展及libjpeg-turbo、zlib、libtiff、libwebp、lcms2；PIL Python对象层主要是调度和对象转换。</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="78" customHeight="1">
+    <x:row r="5" ht="112" customHeight="1">
       <x:c r="A5" s="34" t="str">
         <x:v>SW-004</x:v>
       </x:c>
@@ -1316,7 +1319,7 @@
         <x:v>多次中间 Mat/NumPy buffer、BGR/RGB 与 HWC/CHW 往返；内部线程与其它库超卖</x:v>
       </x:c>
       <x:c r="G5" s="35" t="str">
-        <x:v>组合 resize+color+pad；直接写入目标 buffer；统一线程预算；提供 batch/有限 shape fast path</x:v>
+        <x:v>① 构建启用AArch64 NEON与CPU dispatch的OpenCV版本，在目标机型支持时为resize、颜色转换、normalize等热点评估SVE/SVE2后端；② 融合resize+color+crop/pad+layout转换，直接写入目标Tensor；③ 统一OpenCV、PyTorch和OpenMP/TBB线程预算，避免鲲鹏多核场景过度并行；④ 优化数据对齐、连续访问、预取和NUMA本地内存，降低内存带宽与cache miss。</x:v>
       </x:c>
       <x:c r="H5" s="35" t="str">
         <x:v>公共预处理 pipeline、线程配置矩阵、算子基准</x:v>
@@ -1349,7 +1352,7 @@
         <x:v>主负载：opencv_imgproc SIMD/并行内核；编解码路径继续穿透到libjpeg-turbo、PNG/zlib或FFmpeg；线程开销落在TBB/OpenMP。</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="78" customHeight="1">
+    <x:row r="6" ht="112" customHeight="1">
       <x:c r="A6" s="34" t="str">
         <x:v>SW-005</x:v>
       </x:c>
@@ -1369,7 +1372,7 @@
         <x:v>旧 PIL/NumPy backend 或逐图处理导致慢路径；Tensor 后端未充分利用</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
-        <x:v>统一切到 torchvision Tensor backend；batch/group-by-shape；融合 resize/normalize/dtype/layout；支持 CPU/GPU 可配置执行</x:v>
+        <x:v>① 默认切换到torchvision Tensor/Fast ImageProcessor路径，将PIL/NumPy逐图流程改为批处理或按shape分桶；② 融合resize、normalize、dtype和layout转换，减少ATen small-op及中间Tensor；③ 使用鲲鹏AArch64优化的PyTorch/ATen构建，热点算子采用NEON并在支持机型上评估SVE/SVE2；④ 根据CPU/GPU余量配置CPU、CUDA或其他加速后端，并保留逐模型数值一致性回退。</x:v>
       </x:c>
       <x:c r="H6" s="35" t="str">
         <x:v>Fast ImageProcessor 后端适配、批处理基准、golden parity</x:v>
@@ -1402,7 +1405,7 @@
         <x:v>主负载：PyTorch ATen CPU/CUDA图像算子、libjpeg/libpng解码内核及PyTorch allocator/thread pool；torchvision Python API多为派发。</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="78" customHeight="1">
+    <x:row r="7" ht="112" customHeight="1">
       <x:c r="A7" s="34" t="str">
         <x:v>SW-006</x:v>
       </x:c>
@@ -1422,7 +1425,7 @@
         <x:v>CPU decode/resize 使 GPU 饥饿；但卸载可能与主模型争 GPU</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
-        <x:v>构建 decode→resize→normalize 的批式 pipeline；评估 NVDEC；明确 prefetch、队列深度和 stream 隔离</x:v>
+        <x:v>① 仅在鲲鹏Host连接NVIDIA GPU且AArch64组件支持矩阵满足时启用DALI，形成可选异构后端；② 将decode→resize→normalize组成批式流水线，使用预取和独立stream隐藏CPU准备时间；③ 约束DALI、模型执行与其他CPU库的线程/NUMA资源，避免主模型GPU与Host核竞争；④ CPU fallback统一调用NEON优化的codec/视觉算子，并以端到端SLO决定是否启用GPU卸载。</x:v>
       </x:c>
       <x:c r="H7" s="35" t="str">
         <x:v>DALI 可选后端、CPU/GPU 饱和双场景 A/B、回退路径</x:v>
@@ -1455,7 +1458,7 @@
         <x:v>主负载：DALI C++ operators、nvJPEG/NVDEC、CUDA kernels与copy engine；Python pipeline描述层通常不是主要负载。</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="78" customHeight="1">
+    <x:row r="8" ht="112" customHeight="1">
       <x:c r="A8" s="34" t="str">
         <x:v>SW-007</x:v>
       </x:c>
@@ -1475,7 +1478,7 @@
         <x:v>CPU JPEG/多格式解码重；跨库转换和 D2H/H2D 抵消加速</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
-        <x:v>批量变长图像解码；与 PyTorch/CV-CUDA 零拷贝衔接；复用输出 Image buffer；支持 CPU fallback</x:v>
+        <x:v>① 在鲲鹏+AArch64/NVIDIA部署上验证nvImageCodec、nvJPEG及驱动版本矩阵，不能满足时保留libjpeg-turbo回退；② 批量处理变长图像并复用device/host输出buffer，减少每图提交与同步；③ 与PyTorch/CV-CUDA建立stream-aware少拷贝接口，避免GPU解码后回到Host再转换；④ 将CPU bitstream解析、H2D/D2H和GPU codec分别计量，按真实热点调整线程与NUMA归属。</x:v>
       </x:c>
       <x:c r="H8" s="35" t="str">
         <x:v>可选 GPU codec backend、格式支持矩阵、资源配额</x:v>
@@ -1508,7 +1511,7 @@
         <x:v>主负载：nvJPEG/nvJPEG2K及对应CUDA解码内核、CPU bitstream parser和H2D/D2H拷贝；nvImageCodec主要负责后端选择与调度。</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="78" customHeight="1">
+    <x:row r="9" ht="112" customHeight="1">
       <x:c r="A9" s="34" t="str">
         <x:v>SW-008</x:v>
       </x:c>
@@ -1528,7 +1531,7 @@
         <x:v>小 chunk resample/STFT/log-Mel 的调用、线程调度和中间 Tensor 放大；频繁 open/read 与 dtype 转换增加文件I/O开销</x:v>
       </x:c>
       <x:c r="G9" s="35" t="str">
-        <x:v>有状态 resampler；批量特征；复用 FFT/窗函数；soundfile/libsndfile 路径复用句柄、批量I/O并直接输出目标 dtype</x:v>
+        <x:v>① 将音频文件I/O、重采样、STFT/log-Mel分层，分别选择libsndfile/FFmpeg/TorchCodec和ATen/FFT后端；② 建立有状态流式组件与批量离线组件，复用窗函数、FFT plan、文件句柄和工作buffer；③ 对FIR、窗函数、幅值/功率和dtype转换等DSP热点提供NEON实现，并在支持机型上评估SVE/SVE2向量化；④ 使用连续内存、合理chunk和NUMA本地线程池，避免小块调用与跨socket访问。</x:v>
       </x:c>
       <x:c r="H9" s="35" t="str">
         <x:v>流式音频前处理组件、音频I/O基准、RTF基准、特征与解码 golden</x:v>
@@ -1561,7 +1564,7 @@
         <x:v>主负载：文件I/O穿透到libsndfile、FFmpeg、SoX或TorchCodec；DSP穿透到ATen/FFT/resample内核；torchaudio/soundfile Python层主要派发。</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="78" customHeight="1">
+    <x:row r="10" ht="112" customHeight="1">
       <x:c r="A10" s="34" t="str">
         <x:v>SW-009</x:v>
       </x:c>
@@ -1581,7 +1584,7 @@
         <x:v>重采样实例重复初始化、过小块处理和中间数组导致CPU放大；不同后端的质量/延迟档位未统一</x:v>
       </x:c>
       <x:c r="G10" s="35" t="str">
-        <x:v>提供统一有状态重采样接口；libsoxr与libswresample可选；复用实例；批块处理；直接输出目标采样率/声道/格式</x:v>
+        <x:v>① 统一libsoxr/libswresample适配层，按质量、相位和时延目标选择后端并长期复用重采样状态；② 对多相FIR、样本格式/声道转换等关键负载验证AArch64 NEON路径，在支持机型上增加VLA风格SVE/SVE2实现；③ 批量处理连续chunk、对齐系数和音频buffer，减少边界分支与内存搬运；④ 建立频谱、SNR和相位golden，允许按业务场景配置质量/性能档位。</x:v>
       </x:c>
       <x:c r="H10" s="35" t="str">
         <x:v>统一重采样适配层、质量档位、状态复用、后端A/B与兼容测试</x:v>
@@ -1614,7 +1617,7 @@
         <x:v>主负载：libsoxr或libswresample的滤波、格式/声道转换内核；上层重采样适配器只承担状态管理和派发。</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="78" customHeight="1">
+    <x:row r="11" ht="112" customHeight="1">
       <x:c r="A11" s="34" t="str">
         <x:v>SW-010</x:v>
       </x:c>
@@ -1634,7 +1637,7 @@
         <x:v>chat template、动态分辨率、tiling、placeholder、grid/metadata 和 Python 对象路径成为单核热点</x:v>
       </x:c>
       <x:c r="G11" s="35" t="str">
-        <x:v>分阶段打点；使用 fast/torchvision processor；缓存静态模板与 schema；一次 tokenize；通用数值操作下沉；建立逐模型 fast path</x:v>
+        <x:v>① 将chat template、媒体加载、图像/音频预处理、tokenize和metadata构造拆成独立phase，避免把底层热点归因给Processor入口；② 缓存静态system/tool schema、模板和模型配置，取消重复tokenize与字符串拼接；③ 将像素和Tensor循环下沉到torchvision/ATen的鲲鹏NEON/SVE可派发内核，并按shape分桶批处理；④ 为主流多模态模型建立有限数量的AArch64 fast path，同时保留语义golden和通用回退。</x:v>
       </x:c>
       <x:c r="H11" s="35" t="str">
         <x:v>Processor 性能接口、模型适配清单、golden输入包</x:v>
@@ -1667,7 +1670,7 @@
         <x:v>主负载：图像路径落到torchvision/ATen或Pillow/codec库，文本路径落到HF Tokenizers/SentencePiece，另有Python模板与metadata构造。</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="78" customHeight="1">
+    <x:row r="12" ht="112" customHeight="1">
       <x:c r="A12" s="34" t="str">
         <x:v>SW-011</x:v>
       </x:c>
@@ -1687,7 +1690,7 @@
         <x:v>重复模板后 tokenize、频繁小 batch、tokenizer pool IPC</x:v>
       </x:c>
       <x:c r="G12" s="35" t="str">
-        <x:v>强制 fast tokenizer；batch tokenize；缓存稳定 system/tool schema；减少 offset 等非必要输出；worker 绑核</x:v>
+        <x:v>① 强制采用Rust fast tokenizer并复用encoding/tokenizer实例，长上下文和多请求采用batch接口；② 缓存稳定system/tool schema、静态前缀和模板产物，避免重复规范化与编码；③ 针对UTF-8扫描、字符分类、预分词和批量查表等热点评估AArch64 NEON/SVE2优化或升级到已优化的Rust依赖；④ 按NUMA部署tokenizer worker并减少IPC原文传输，形成可观测的worker池与背压策略。</x:v>
       </x:c>
       <x:c r="H12" s="35" t="str">
         <x:v>Tokenizer 服务/池、长上下文基准、版本化缓存</x:v>
@@ -1720,7 +1723,7 @@
         <x:v>主负载：Hugging Face tokenizers Rust core的预分词、模型查找和后处理；Python binding与对象封装通常为次要负载。</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="78" customHeight="1">
+    <x:row r="13" ht="112" customHeight="1">
       <x:c r="A13" s="34" t="str">
         <x:v>SW-012</x:v>
       </x:c>
@@ -1740,7 +1743,7 @@
         <x:v>小批处理、重复初始化和 Python binding 调用放大</x:v>
       </x:c>
       <x:c r="G13" s="35" t="str">
-        <x:v>进程内模型复用；批量编码/解码；C++ fast path；避免跨进程传原始字符串</x:v>
+        <x:v>① 进程内复用SentencePiece模型和normalizer，批量执行encode/decode并减少Python binding往返；② 将规范化、UTF-8扫描、前缀查找和结果写出作为关键模块进行AArch64 profiling，对适合的数据扫描路径实施NEON/SVE2向量化；③ 预留输出容量并复用工作内存，减少短命string/vector分配；④ tokenizer pool按鲲鹏NUMA节点部署，避免跨进程传输长文本和重复加载模型。</x:v>
       </x:c>
       <x:c r="H13" s="35" t="str">
         <x:v>统一 SentencePiece adapter、micro/端到端基准</x:v>
@@ -1773,7 +1776,7 @@
         <x:v>主负载：SentencePiece C++ normalization、Unigram/BPE编码解码内核；Python binding主要负责参数转换和结果封装。</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="78" customHeight="1">
+    <x:row r="14" ht="112" customHeight="1">
       <x:c r="A14" s="34" t="str">
         <x:v>SW-013</x:v>
       </x:c>
@@ -1793,7 +1796,7 @@
         <x:v>频繁单条编码、重复schema文本和字符串转换</x:v>
       </x:c>
       <x:c r="G14" s="35" t="str">
-        <x:v>batch接口；静态前缀缓存；复用encoding实例；减少bytes/string往返</x:v>
+        <x:v>① 复用tiktoken encoding实例，对长文本和多请求使用batch接口并缓存静态前缀/tool schema；② 将regex切分、字节分类、UTF-8验证和BPE查找分别profile，对Rust原生热点采用AArch64 NEON/SVE2可用实现；③ 减少Python bytes/string转换与结果对象数量，提供紧凑token buffer接口；④ worker按NUMA绑核并限定并发，避免regex线程、服务worker和其他tokenizer池相互争抢。</x:v>
       </x:c>
       <x:c r="H14" s="35" t="str">
         <x:v>tiktoken adapter、前缀缓存、基准</x:v>
@@ -1826,7 +1829,7 @@
         <x:v>主负载：tiktoken Rust core的regex切分、BPE merge与查表；Python入口自身通常占比低。</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="78" customHeight="1">
+    <x:row r="15" ht="112" customHeight="1">
       <x:c r="A15" s="34" t="str">
         <x:v>SW-014</x:v>
       </x:c>
@@ -1846,7 +1849,7 @@
         <x:v>small-op、dispatcher、stack/concat、contiguous和dtype cast造成多次分配和全量内存遍历</x:v>
       </x:c>
       <x:c r="G15" s="35" t="str">
-        <x:v>from-buffer/共享storage；预分配；批量collate；消除重复contiguous/cast；限定shape桶</x:v>
+        <x:v>① 采用鲲鹏AArch64优化的PyTorch/ATen构建，核查native kernel、oneDNN/ACL等真实后端，避免落到reference实现；② 合并stack/concat/cast/contiguous等small-op，建立from-buffer、预分配和有限shape批处理fast path；③ 对normalize、layout、reduce、copy等内存型热点启用NEON并按机型评估SVE/SVE2，对辅助模型评估BF16/INT8；④ 统一dispatcher、allocator和线程池策略，结合NUMA本地内存与cache miss指标优化。</x:v>
       </x:c>
       <x:c r="H15" s="35" t="str">
         <x:v>Host Tensor fast path、算子profile、内存拷贝审计</x:v>
@@ -1879,7 +1882,7 @@
         <x:v>主负载：ATen native CPU kernels、oneDNN/FFT后端、OpenMP线程池、allocator与memcpy；dispatcher只在small-op密集时成为独立热点。</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="78" customHeight="1">
+    <x:row r="16" ht="112" customHeight="1">
       <x:c r="A16" s="34" t="str">
         <x:v>SW-015</x:v>
       </x:c>
@@ -1899,7 +1902,7 @@
         <x:v>Python/dispatcher开销和多算子内存往返；动态shape导致graph break/recompile</x:v>
       </x:c>
       <x:c r="G16" s="35" t="str">
-        <x:v>对有限shape桶编译；融合normalize/layout/pad；预热与缓存编译产物；记录graph break</x:v>
+        <x:v>① 为稳定的预处理/后处理Tensor子图建立AArch64编译清单和shape桶，避免graph break与重复编译；② 确认生成的C++/OpenMP内核面向实际鲲鹏CPU编译并实现NEON自动向量化，支持机型再启用SVE/SVE2 VLA代码；③ 融合逐元素、layout、pad和normalize操作，降低内存遍历次数；④ 建立编译缓存、预热、PGO/LTO可行性评估和eager回退，网络I/O与高度动态Python逻辑不纳入强制编译。</x:v>
       </x:c>
       <x:c r="H16" s="35" t="str">
         <x:v>可编译子图清单、编译缓存、回退机制</x:v>
@@ -1932,7 +1935,7 @@
         <x:v>主负载：生成的C++/OpenMP CPU kernel或Triton/CUDA kernel；graph break路径回落到ATen。Inductor编译器主要影响首编译和重编译。</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="78" customHeight="1">
+    <x:row r="17" ht="112" customHeight="1">
       <x:c r="A17" s="34" t="str">
         <x:v>SW-016</x:v>
       </x:c>
@@ -1952,7 +1955,7 @@
         <x:v>线程超卖、NUMA、layout重排和未融合图使CPU辅助模型拖尾</x:v>
       </x:c>
       <x:c r="G17" s="35" t="str">
-        <x:v>统一线程池与affinity；图融合；固定layout；INT8/BF16评估；按GPU本地NUMA部署</x:v>
+        <x:v>① 在鲲鹏AArch64构建中启用oneDNN的ACL集成或可用的ARM优化后端，避免reference primitive；② 固化辅助模型常用shape和layout，复用primitive/weight pack并融合post-op、reorder与量化算子；③ 根据目标机型选择NEON、SVE/BF16等可用内核，不支持时保持正确的多版本派发；④ 统一OpenMP/TBB/threadpool运行时、绑核和NUMA策略，避免oneDNN与PyTorch/OpenCV线程池叠加。</x:v>
       </x:c>
       <x:c r="H17" s="35" t="str">
         <x:v>辅助模型后端配置、拓扑基准、精度报告</x:v>
@@ -1985,7 +1988,7 @@
         <x:v>主负载：oneDNN primitive/JIT SIMD kernel、reorder以及其线程运行时；PyTorch/ORT/OpenVINO通常只是调用入口。</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="78" customHeight="1">
+    <x:row r="18" ht="112" customHeight="1">
       <x:c r="A18" s="34" t="str">
         <x:v>SW-017</x:v>
       </x:c>
@@ -2005,7 +2008,7 @@
         <x:v>execution provider、batch、线程和量化未优化；同步调用阻塞主链路</x:v>
       </x:c>
       <x:c r="G18" s="35" t="str">
-        <x:v>选择合适EP；模型图优化/量化；动态合批；独立线程池；超时降级和缓存</x:v>
+        <x:v>① 建立ONNX Runtime鲲鹏AArch64发行版，按模型选择实际可用的MLAS、ACL/oneDNN或供应商Execution Provider，禁止默认落入reference kernel而不告警；② 做图优化、常量折叠、算子融合、固定shape/内存pattern和INT8/BF16评估；③ 对CPU辅助模型建立动态合批、独立线程池、NUMA绑核与模型常驻机制；④ 输出EP级别算子覆盖和fallback清单，把未覆盖热点下沉到NEON/SVE优化算子或替代后端。</x:v>
       </x:c>
       <x:c r="H18" s="35" t="str">
         <x:v>ORT运行时封装、模型优化包、质量/性能报告</x:v>
@@ -2038,7 +2041,7 @@
         <x:v>主负载：所选Execution Provider的MLAS、oneDNN、OpenVINO、CUDA或TensorRT kernel，以及ORT thread pool；ORT API层主要调度。</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="78" customHeight="1">
+    <x:row r="19" ht="112" customHeight="1">
       <x:c r="A19" s="34" t="str">
         <x:v>SW-018</x:v>
       </x:c>
@@ -2058,7 +2061,7 @@
         <x:v>未利用Intel图优化/量化，线程与NUMA配置不当</x:v>
       </x:c>
       <x:c r="G19" s="35" t="str">
-        <x:v>为Intel平台提供可选EP；INT8；吞吐/延迟模式；绑核与多stream；与ORT统一接口</x:v>
+        <x:v>① OpenVINO以Intel平台为主要优化对象，在鲲鹏部署中不得作为默认性能后端；② 若业务必须保持统一接口，应先完成AArch64兼容性和算子覆盖验证，并通过同口径基准与ORT/ACL/oneDNN ARM路径比较；③ 对鲲鹏生产环境优先选择原生AArch64 Execution Provider，避免为平台不匹配的runtime投入深度优化；④ 保留模型语义、量化精度和跨平台回退，按部署平台分别发布配置。</x:v>
       </x:c>
       <x:c r="H19" s="35" t="str">
         <x:v>OpenVINO backend、平台基准、回退路径</x:v>
@@ -2091,7 +2094,7 @@
         <x:v>主负载：OpenVINO device plugin及oneDNN/ACL/设备内核；OpenVINO API与ORT EP适配层不应单独承接全部热点。</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="78" customHeight="1">
+    <x:row r="20" ht="112" customHeight="1">
       <x:c r="A20" s="34" t="str">
         <x:v>SW-019</x:v>
       </x:c>
@@ -2111,7 +2114,7 @@
         <x:v>mm processor、hash/cache、prompt update、scheduler、API↔engine IPC与输出状态机成为Host热点</x:v>
       </x:c>
       <x:c r="G20" s="35" t="str">
-        <x:v>接入mm-processor分段指标；优化processor cache；多模态成本模型；CPU-ready batching；紧凑IPC；阶段级背压</x:v>
+        <x:v>① 将mm processor、hash/cache、prompt update、scheduler、IPC和输出循环按phase拆开，分别归因到真实底层库；② 缓存多模态processor结果、静态tool schema和tokenization产物，使用成本感知分桶与CPU-ready batching；③ 在鲲鹏上将热点Python状态机/对象循环下沉到Rust/C++原生模块，并使用AArch64优化的tokenizer、JSON、codec和Tensor库；④ worker、共享内存、pinned buffer与GPU按NUMA拓扑部署，形成ARM64 wheel/容器和持续回归基线。</x:v>
       </x:c>
       <x:c r="H20" s="35" t="str">
         <x:v>vLLM多模态性能基线、patch/配置包、回归集</x:v>
@@ -2144,7 +2147,7 @@
         <x:v>主负载：vLLM scheduler/state machine、HF Processor、torchvision/Pillow、tokenizer、hash/serialization/IPC及CUDA runtime；必须按phase拆分归属。</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="78" customHeight="1">
+    <x:row r="21" ht="112" customHeight="1">
       <x:c r="A21" s="34" t="str">
         <x:v>SW-020</x:v>
       </x:c>
@@ -2164,7 +2167,7 @@
         <x:v>scheduler、Radix/prefix cache、request state、IPC和输出循环在异构请求下放大</x:v>
       </x:c>
       <x:c r="G21" s="35" t="str">
-        <x:v>多模态成本估算与分桶；cache收益核算；减少Python状态；结构化输出编译缓存；统一phase tracing</x:v>
+        <x:v>① 对scheduler、Radix/prefix cache、request state、grammar和output loop建立分段exclusive-time指标；② 多模态请求按媒体成本和shape分桶，减少Python对象状态与跨进程metadata；③ 在鲲鹏上优先使用AArch64原生tokenizer、JSON parser、xgrammar和hash实现，适合的bitset/扫描模块采用NEON/SVE2优化；④ cache、worker、IPC和GPU按NUMA节点配置，并保持与vLLM相同的语义golden和跨框架基准。</x:v>
       </x:c>
       <x:c r="H21" s="35" t="str">
         <x:v>SGLang性能基线、配置策略、回归集</x:v>
@@ -2197,7 +2200,7 @@
         <x:v>主负载：SGLang scheduler、Radix/prefix cache、request状态机、tokenizer/processor、grammar backend、IPC及CUDA runtime；框架总耗时需继续下钻。</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="78" customHeight="1">
+    <x:row r="22" ht="112" customHeight="1">
       <x:c r="A22" s="34" t="str">
         <x:v>SW-021</x:v>
       </x:c>
@@ -2217,7 +2220,7 @@
         <x:v>ensemble与动态批处理若不了解媒体成本会形成队头阻塞和跨模型排队</x:v>
       </x:c>
       <x:c r="G22" s="35" t="str">
-        <x:v>拆分媒体/processor/模型实例组；明确队列与batch策略；使用共享内存；按阶段独立扩缩容</x:v>
+        <x:v>① 只有在Triton Server及目标backend具备受支持的AArch64版本时才在鲲鹏部署，并形成明确版本矩阵；② 将媒体、processor和模型backend拆分实例组，分别配置队列、动态batch和CPU亲和性；③ 使用共享内存/零拷贝减少gRPC/HTTP与backend之间的大对象序列化，按NUMA放置共享区和worker；④ 将Triton调度开销与TensorRT/ORT/PyTorch等真实backend负载分开验收。</x:v>
       </x:c>
       <x:c r="H22" s="35" t="str">
         <x:v>Triton部署模板、队列/实例组基准、监控面板</x:v>
@@ -2250,7 +2253,7 @@
         <x:v>主负载：具体Triton backend（TensorRT/ORT/PyTorch/Python）、dynamic batcher、共享内存/网络栈；ensemble配置层主要调度。</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="78" customHeight="1">
+    <x:row r="23" ht="112" customHeight="1">
       <x:c r="A23" s="34" t="str">
         <x:v>SW-022</x:v>
       </x:c>
@@ -2270,7 +2273,7 @@
         <x:v>Host提交、调度和前后处理未与TensorRT-LLM执行节奏协同</x:v>
       </x:c>
       <x:c r="G23" s="35" t="str">
-        <x:v>对齐CPU-ready批处理；减少Host同步；紧凑输入descriptor；按阶段profile；与codec/processor服务解耦</x:v>
+        <x:v>① 在鲲鹏Host连接NVIDIA GPU的场景验证TensorRT-LLM ARM64、CUDA和驱动兼容矩阵；② 将CPU-ready batch、输入descriptor和输出状态机下沉到C++路径，减少Python调度与Host同步；③ 建立pinned buffer池、合并小tensor并使用独立copy stream，按PCIe/GPU所在NUMA节点绑定CPU和内存；④ 分离TensorRT-LLM Host runtime、tokenizer/processor和CUDA提交阶段，按真实热点实施优化。</x:v>
       </x:c>
       <x:c r="H23" s="35" t="str">
         <x:v>TensorRT-LLM Host基线、集成适配、回归集</x:v>
@@ -2303,7 +2306,7 @@
         <x:v>主负载：TensorRT-LLM C++ runtime、TensorRT/CUDA driver/runtime、NCCL及Host数据准备；Python serving入口通常不是计算热点。</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="78" customHeight="1">
+    <x:row r="24" ht="112" customHeight="1">
       <x:c r="A24" s="34" t="str">
         <x:v>SW-023</x:v>
       </x:c>
@@ -2323,7 +2326,7 @@
         <x:v>grammar编译和每token状态更新使TPOT上升</x:v>
       </x:c>
       <x:c r="G24" s="35" t="str">
-        <x:v>canonical schema与编译缓存；C++增量状态机；复用token mask；暴露compile/update阶段指标</x:v>
+        <x:v>① 缓存canonical JSON Schema、CFG编译结果和tokenizer映射，避免每请求重复构建；② 将grammar matcher、增量状态机和token mask/bitset更新稳定在C++原生路径；③ 对大词表bitset、字节扫描和mask合并等数据并行模块实施AArch64 NEON优化，并在支持机型上评估SVE/SVE2；④ 提供batch状态更新、紧凑内存布局和NUMA本地缓存，同时守护结构化成功率与TPOT。</x:v>
       </x:c>
       <x:c r="H24" s="35" t="str">
         <x:v>grammar runtime封装、缓存、兼容/性能集</x:v>
@@ -2356,7 +2359,7 @@
         <x:v>主负载：xgrammar C++ grammar compiler、matcher、token mask更新及tokenizer映射；Python binding主要负责接入。</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="78" customHeight="1">
+    <x:row r="25" ht="112" customHeight="1">
       <x:c r="A25" s="34" t="str">
         <x:v>SW-024</x:v>
       </x:c>
@@ -2376,7 +2379,7 @@
         <x:v>Python层schema构造、FSM编译与集成开销</x:v>
       </x:c>
       <x:c r="G25" s="35" t="str">
-        <x:v>缓存编译结果；预生成常用schema；减少Python callback；与xgrammar做同口径基准</x:v>
+        <x:v>① 将Outlines限定为schema/策略入口，编译和逐token FSM执行优先下沉到outlines-core、xgrammar或其他原生backend；② 缓存常用schema、regex和FSM产物，减少Python callback与对象分配；③ backend中的扫描、bitset和token过滤热点采用AArch64 NEON/SVE2可用实现；④ 与xgrammar做同口径compile、update和TPOT基准，避免维护多套不一致的grammar语义。</x:v>
       </x:c>
       <x:c r="H25" s="35" t="str">
         <x:v>Outlines adapter、schema缓存、对比报告</x:v>
@@ -2409,7 +2412,7 @@
         <x:v>主负载：Outlines Python schema/FSM构造及所选native backend（如outlines-core/xgrammar/regex）；需按实际backend归因。</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="78" customHeight="1">
+    <x:row r="26" ht="112" customHeight="1">
       <x:c r="A26" s="34" t="str">
         <x:v>SW-025</x:v>
       </x:c>
@@ -2429,7 +2432,7 @@
         <x:v>pageable→pinned、频繁分配、小块H2D、默认stream和隐式同步造成GPU等待</x:v>
       </x:c>
       <x:c r="G26" s="35" t="str">
-        <x:v>pinned buffer池；直接产出pinned；合并小tensor；non_blocking；独立copy stream/event；清理.item/.cpu同步</x:v>
+        <x:v>① 在鲲鹏Host+GPU拓扑上建立pageable、pinned、H2D和同步的分段基线；② 使用分级pinned buffer池，媒体/Processor直接产出pinned memory，并合并小tensor和小copy；③ 通过non_blocking、独立copy stream/event实现准备与执行重叠，清理.item/.cpu等隐式同步；④ 按GPU所在NUMA节点绑定分配线程和内存，优化连续访问、cache line对齐和生命周期，避免过度pin导致系统抖动。</x:v>
       </x:c>
       <x:c r="H26" s="35" t="str">
         <x:v>Host staging组件、拓扑策略、Nsight/PyTorch trace基线</x:v>
@@ -2462,7 +2465,7 @@
         <x:v>主负载：PyTorch pinned allocator、CUDA runtime/driver、libc memcpy以及DMA/copy engine；non_blocking API本身仅提交与同步。</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="78" customHeight="1">
+    <x:row r="27" ht="112" customHeight="1">
       <x:c r="A27" s="34" t="str">
         <x:v>SW-026</x:v>
       </x:c>
@@ -2482,7 +2485,7 @@
         <x:v>短生命周期对象与帧buffer导致allocator锁、碎片、RSS和page fault</x:v>
       </x:c>
       <x:c r="G27" s="35" t="str">
-        <x:v>做allocator A/B；buffer pool/size class；减少短命对象；按NUMA first-touch；记录RSS/active</x:v>
+        <x:v>① 在鲲鹏真实并发和对象尺寸分布上比较glibc/kpglibc、jemalloc、tcmalloc和mimalloc，选择可回退的生产配置；② 对帧buffer、Tensor metadata、JSON对象等高频尺寸建立对象池/size class并减少短命分配；③ allocator arena、worker和内存按NUMA节点对齐，控制跨socket free、锁竞争与RSS碎片；④ 结合大页/THP、first-touch和内存回收策略做A/B，以P99、page fault和RSS而非单一microbenchmark验收。</x:v>
       </x:c>
       <x:c r="H27" s="35" t="str">
         <x:v>内存基准、推荐allocator与配置、碎片监控</x:v>
@@ -2515,7 +2518,7 @@
         <x:v>主负载：实际生效的glibc malloc、jemalloc、tcmalloc或mimalloc的分配/回收/锁/arena，以及Linux page fault；调用方只触发。</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="78" customHeight="1">
+    <x:row r="28" ht="112" customHeight="1">
       <x:c r="A28" s="34" t="str">
         <x:v>SW-027</x:v>
       </x:c>
@@ -2535,7 +2538,7 @@
         <x:v>FFmpeg/OpenCV/PyTorch/oneDNN/tokenizer各自开池导致oversubscription和上下文切换</x:v>
       </x:c>
       <x:c r="G28" s="35" t="str">
-        <x:v>建立整机线程预算；按阶段隔离池；绑核；避免嵌套并行；运行时导出线程配置与run queue指标</x:v>
+        <x:v>① 基于鲲鹏多核/NUMA拓扑建立全进程线程预算，统一OpenMP、oneTBB、pthread、codec、PyTorch和tokenizer线程池；② 禁止嵌套并行与oversubscription，按阶段选择串行、批内并行或请求级并行；③ worker按NUMA和GPU亲和性绑核，调节任务粒度、队列、spin/sleep策略和背压；④ 对NEON/SVE计算核与内存型核分别评估扩展效率，以吞吐/核、run queue和context switch确定并发上限。</x:v>
       </x:c>
       <x:c r="H28" s="35" t="str">
         <x:v>线程预算控制器、硬件配置模板、扩展性基准</x:v>
@@ -2568,7 +2571,7 @@
         <x:v>主负载：libgomp/libomp/oneTBB/pthread/futex的调度开销，以及各调用库worker中的真实算子；必须区分runtime overhead与worker work。</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="78" customHeight="1">
+    <x:row r="29" ht="112" customHeight="1">
       <x:c r="A29" s="34" t="str">
         <x:v>SW-028</x:v>
       </x:c>
@@ -2588,7 +2591,7 @@
         <x:v>worker、内存和GPU PCIe根节点错位造成远端访问与H2D下降</x:v>
       </x:c>
       <x:c r="G29" s="35" t="str">
-        <x:v>按GPU绑CPU和内存；first-touch预热；限制跨socket共享；在调度器中传递拓扑信息</x:v>
+        <x:v>① 服务启动时探测鲲鹏socket、NUMA、内存控制器、PCIe和GPU拓扑，并将信息传递给调度器；② worker、线程池、buffer pool、模型权重和共享内存采用first-touch及NUMA本地分配，减少remote memory；③ 将GPU相关预处理、pinned分配和H2D线程绑定到对应PCIe根节点，跨socket共享只保留必要的只读数据；④ 评估大页、内存交织和容器/cgroup绑核策略，以remote NUMA%、带宽和P99验收。</x:v>
       </x:c>
       <x:c r="H29" s="35" t="str">
         <x:v>NUMA部署策略、拓扑探测、跨拓扑A/B</x:v>
@@ -2621,7 +2624,7 @@
         <x:v>主负载：调用库中的内存访问、libc memcpy、Linux mm/page fault及远端NUMA流量；NUMA binding API自身不是计算热点。</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="78" customHeight="1">
+    <x:row r="30" ht="112" customHeight="1">
       <x:c r="A30" s="34" t="str">
         <x:v>SW-029</x:v>
       </x:c>
@@ -2641,7 +2644,7 @@
         <x:v>同步CPU任务阻塞event loop；Pydantic对象、base64和逐token SSE造成CPU/尾延迟</x:v>
       </x:c>
       <x:c r="G30" s="35" t="str">
-        <x:v>CPU任务移出event loop；schema fast path；分块解析；自适应SSE chunk；慢客户端隔离；worker分层</x:v>
+        <x:v>① 将请求解析、Pydantic校验、base64/媒体读取、业务处理和SSE输出分阶段打点，CPU重任务移出event loop；② 带Schema请求直接使用Pydantic-core（含jiter）的model_validate_json等融合路径，通用dict/list响应与SSE封包使用orjson，禁止默认采用orjson.loads→Pydantic再次遍历的重复路径；③ 在鲲鹏上使用AArch64原生Pydantic-core、orjson、uvloop/httptools和优化TLS库，减少Python对象与bytes/string往返；④ worker按NUMA部署并实施连接、慢客户端和大媒体请求隔离。</x:v>
       </x:c>
       <x:c r="H30" s="35" t="str">
         <x:v>API fast path、压力测试、事件循环监控</x:v>
@@ -2671,63 +2674,63 @@
         <x:v>上层入口/服务适配层</x:v>
       </x:c>
       <x:c r="Q30" s="58" t="str">
-        <x:v>主负载：Pydantic-core、orjson、uvloop/libuv、httptools/h11、asyncio任务调度、OpenSSL及内核网络栈；FastAPI路由层常是入口而非最终热点。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="78" customHeight="1">
+        <x:v>主负载：带Schema请求/结构化输出落到Pydantic-core（jiter解析、validator与Python对象构造）；通用dict/list响应与SSE JSON落到orjson；其余为uvloop/libuv、httptools/h11、OpenSSL及Linux网络栈。FastAPI路由层主要是入口。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="190" customHeight="1">
       <x:c r="A31" s="34" t="str">
         <x:v>SW-030</x:v>
       </x:c>
       <x:c r="B31" s="35" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="C31" s="35" t="str">
-        <x:v>orjson / Protobuf / gRPC</x:v>
+        <x:v>Pydantic-core（含jiter）/ orjson / simdjson / RapidJSON / sonic-cpp / Protobuf / gRPC</x:v>
       </x:c>
       <x:c r="D31" s="35" t="str">
-        <x:v>序列化与IPC</x:v>
+        <x:v>JSON解析、Schema校验、序列化与IPC</x:v>
       </x:c>
       <x:c r="E31" s="35" t="str">
-        <x:v>请求响应、跨进程消息、流式输出</x:v>
+        <x:v>AI推理请求/响应、Agent tool_call、Structured Output、JSON mode、SSE及跨进程消息</x:v>
       </x:c>
       <x:c r="F31" s="35" t="str">
-        <x:v>大JSON、logprobs、多模态metadata、重复bytes/string转换和逐token编码</x:v>
+        <x:v>Schema化JSON、通用JSON和流式碎片混用；orjson.loads后再Pydantic校验、model_dump后再dumps等重复遍历；逐token重扫历史buffer；字符串/UTF-8/数字处理、Python对象构造、Schema校验及bytes/string复制共同放大CPU、TTFT/TPOT和P99</x:v>
       </x:c>
       <x:c r="G31" s="35" t="str">
-        <x:v>内部改二进制协议；复用buffer；增量字段；批量/分块序列化；只传紧凑metadata</x:v>
+        <x:v>① 建立统一JSON处理规范但按执行场景分层：P0优先Pydantic-core（含jiter）承载Schema驱动解析、类型转换、Structured Output/tool_call校验及partial JSON；P0优先orjson承载普通dict/list、SSE、metadata和日志等通用Python序列化；P1以simdjson承载C/C++网关、大JSON及On-Demand字段投影。② 消除重复链路：带Schema输入优先直接model_validate_json，Pydantic模型优先直接model_dump_json；只有已经是通用Python对象时才进入orjson，禁止默认叠加两套解析/序列化。③ 鲲鹏侧针对真实热点建设AArch64原生构建：jiter/原生parser优化结构扫描、partial状态、字段查找、validator和对象构造；orjson优化字符串转义、UTF-8、数字格式化及一次性bytes输出；simdjson强化NEON structural scan与On-Demand，SVE/SVE2仅按机型派发。④ RapidJSON仅做生产存量兼容和热点定点优化；sonic-cpp在ARM后端成熟且有明确业务采用后再支持，不投入五套同类内核。⑤ 内部高频IPC优先Protobuf/gRPC紧凑消息和buffer复用，避免用JSON传递大tensor或重复metadata。</x:v>
       </x:c>
       <x:c r="H31" s="35" t="str">
-        <x:v>序列化基准、IPC schema、兼容层</x:v>
+        <x:v>JSON调用规范与库选型矩阵、Pydantic-core/jiter Agent fast path、orjson响应/SSE fast path、simdjson ARM基准与适配、重复解析审计、Schema缓存、IPC schema及场景分层golden/benchmark</x:v>
       </x:c>
       <x:c r="I31" s="35" t="str">
-        <x:v>µs/KB；allocations；IPC bytes；writes；P99</x:v>
+        <x:v>各场景CPU/request与exclusive time；parse/validate/serialize µs/KB；µs/token；历史buffer重复扫描bytes；Python allocations；中间dict/list数量；copy bytes；SSE writes；IPC bytes；TTFT/TPOT/P99；语义与错误恢复一致性</x:v>
       </x:c>
       <x:c r="J31" s="35" t="str">
-        <x:v>序列化或IPC占CPU链路&gt;10%</x:v>
+        <x:v>AI Agent的tool_call/Structured Output进入主链路，或JSON解析+校验+序列化累计占HOST CPU≥5%，或重复解析/对象构造进入CPU Top-N；simdjson、RapidJSON、sonic-cpp仍须分别由生产调用链和流量证明</x:v>
       </x:c>
       <x:c r="K31" s="35" t="str">
-        <x:v>平台中间件团队</x:v>
+        <x:v>平台中间件团队 / Agent基础设施团队</x:v>
       </x:c>
       <x:c r="L31" s="35" t="str">
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="M31" s="35" t="str">
-        <x:v>协议演进和多语言兼容需要版本管理</x:v>
+        <x:v>库benchmark不可代替端到端收益；partial JSON不等于跨chunk零重扫，必须验证实际API；不得绕过Schema、安全校验、Unicode/数字和错误语义；RapidJSON存量与sonic-cpp ARM能力不得按star或x86 benchmark直接升档</x:v>
       </x:c>
       <x:c r="N31" s="36" t="str">
-        <x:v>https://grpc.io/docs/</x:v>
+        <x:v>https://docs.pydantic.dev/latest/concepts/json/ ; https://github.com/pydantic/jiter ; https://github.com/ijl/orjson ; https://github.com/simdjson/simdjson ; https://github.com/Tencent/rapidjson ; https://github.com/bytedance/sonic-cpp ; https://grpc.io/docs/</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>开源社区/厂商主导开源混合｜跨硬件、协议级</x:v>
+        <x:v>主支持库均为开源社区项目且跨厂商；Pydantic-core/jiter与orjson偏Python生态，simdjson跨语言；RapidJSON为广泛历史存量；sonic-cpp当前ARM成熟度受限但非硬件厂商专有；Protobuf/gRPC跨硬件</x:v>
       </x:c>
       <x:c r="P31" s="58" t="str">
-        <x:v>适配层+原生执行内核</x:v>
+        <x:v>上层适配/Schema执行层 + 底层解析/序列化内核 + IPC执行层</x:v>
       </x:c>
       <x:c r="Q31" s="58" t="str">
-        <x:v>主负载：orjson Rust core、protobuf C++/upb、gRPC core/HTTP2、OpenSSL和libc memcpy；Python stub与message wrapper多为调用入口。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="78" customHeight="1">
+        <x:v>主要真实负载按场景归因：Schema请求、tool_call和Structured Output落到Pydantic-core（jiter、validator、serializer及Python对象构造）；普通Python响应/SSE落到orjson；C/C++大JSON和字段投影落到simdjson；RapidJSON仅在存量调用命中时归因，sonic-cpp仅在ARM生产路径启用后归因；IPC落到protobuf/gRPC core、TLS和libc memcpy。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="112" customHeight="1">
       <x:c r="A32" s="34" t="str">
         <x:v>SW-031</x:v>
       </x:c>
@@ -2747,7 +2750,7 @@
         <x:v>远端缓存原始tensor序列化成本高；本地多进程重复；低命中时hash/lookup成为纯开销，且常与序列化和内存拷贝混在一起</x:v>
       </x:c>
       <x:c r="G32" s="35" t="str">
-        <x:v>分层缓存；大对象优先shared memory/本地；Redis存metadata/冷层；非安全缓存键优先xxHash；安全/完整性需求使用OpenSSL EVP或BLAKE3；避免重复序列化与重复hash</x:v>
+        <x:v>① 按processor结果、媒体metadata、会话和扩展KV建立分层缓存，先核算命中净收益再决定远端/本地层；② cache key一次canonicalize并一次hash，非安全场景优先xxHash，安全完整性使用OpenSSL/BLAKE3，避免序列化后重复扫描；③ 对大buffer hash、copy和校验采用AArch64 NEON并按机型评估SVE/SVE2，复用连续buffer；④ shared memory、Redis client/server和LMCache worker按NUMA部署，建立容量、淘汰、版本隔离和错误命中保护。</x:v>
       </x:c>
       <x:c r="H32" s="35" t="str">
         <x:v>缓存分层方案、hash/序列化/拷贝分段基准、容量模型、命中与净收益看板</x:v>
@@ -2780,7 +2783,7 @@
         <x:v>主负载：xxHash/OpenSSL/BLAKE3、序列化与memcpy、Redis server/network、shared-memory拷贝及LMCache具体backend；cache API耗时需拆成子阶段。</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="78" customHeight="1">
+    <x:row r="33" ht="112" customHeight="1">
       <x:c r="A33" s="34" t="str">
         <x:v>SW-032</x:v>
       </x:c>
@@ -2800,7 +2803,7 @@
         <x:v>per-token span、高基数label、原始媒体/长文本日志污染P99并扭曲profile</x:v>
       </x:c>
       <x:c r="G33" s="35" t="str">
-        <x:v>定义固定phase指标；采样聚合；高基数转事件；禁止base64；异步批写；区分低开销/诊断模式</x:v>
+        <x:v>① 将可观测性拆成常驻低开销模式与限时诊断模式，禁止per-token全量span和高基数label；② 使用每线程/每核buffer、采样聚合和异步批量export，减少锁、分配和同步I/O；③ 复用Protobuf/JSON buffer并采用AArch64原生序列化/TLS实现，严禁记录base64媒体和长prompt；④ 将OTel SDK、序列化、exporter和网络分别计量，控制在明确CPU/P99预算内。</x:v>
       </x:c>
       <x:c r="H33" s="35" t="str">
         <x:v>统一phase tracing规范、指标面板、开销基准</x:v>
@@ -2833,7 +2836,7 @@
         <x:v>主负载：OTel SDK聚合/锁/分配、Protobuf/JSON序列化、exporter网络I/O及Prometheus采集；业务埋点函数通常只是入口。</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="78" customHeight="1">
+    <x:row r="34" ht="112" customHeight="1">
       <x:c r="A34" s="34" t="str">
         <x:v>SW-033</x:v>
       </x:c>
@@ -2853,7 +2856,7 @@
         <x:v>缺少统一阶段归因，单看CPU利用率或cudaMemcpy无法定位owner</x:v>
       </x:c>
       <x:c r="G34" s="35" t="str">
-        <x:v>统一marker与request/phase关联；CPU flame graph、调度/IPC/H2D/GPU gap联合分析；建立自动回归</x:v>
+        <x:v>① 建立适用于鲲鹏AArch64的统一profiling流水线，包含perf/eBPF、PyTorch Profiler及GPU场景的Nsight，保留build-id与原生符号；② 同时输出inclusive/exclusive time、DSO/.so、线程池、实际backend和调用链，识别上层穿透；③ 使用ARM PMU观察IPC、分支、L1/L2/LLC、TLB、内存带宽和remote NUMA，并验证NEON/SVE向量化是否真正生效；④ 将标准trace和关键microbenchmark纳入持续回归，限制profiling开销。</x:v>
       </x:c>
       <x:c r="H34" s="35" t="str">
         <x:v>profiling工具链、标准trace、自动回归门禁</x:v>
@@ -2886,7 +2889,7 @@
         <x:v>该行不承接业务负载：perf/eBPF/Nsight/PyTorch Profiler负责观测；真实热点应归属采样命中的DSO、native symbol、线程池或GPU kernel。</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="78" customHeight="1">
+    <x:row r="35" ht="112" customHeight="1">
       <x:c r="A35" s="34" t="str">
         <x:v>SW-034</x:v>
       </x:c>
@@ -2906,7 +2909,7 @@
         <x:v>CPU H.264/H.265编码成为GPU完成后的主尾部瓶颈</x:v>
       </x:c>
       <x:c r="G35" s="35" t="str">
-        <x:v>硬件编码池；异步编码；质量/码率档位；帧buffer零/少拷贝；与主模型GPU资源隔离</x:v>
+        <x:v>① 仅在鲲鹏Host连接支持NVENC的NVIDIA GPU时启用，验证ARM64驱动与Video Codec SDK版本矩阵；② 使用硬件编码池、异步队列和固定质量/码率档位，避免CPU软件编码成为输出尾部瓶颈；③ 复用surface和host/device buffer，尽量保持GPU侧格式转换并减少D2H/H2D；④ 编码提交线程、pinned内存和GPU按NUMA拓扑部署，与主模型GPU资源隔离并保留软件编码回退。</x:v>
       </x:c>
       <x:c r="H35" s="35" t="str">
         <x:v>NVENC输出backend、资源调度、质量/性能报告</x:v>
@@ -2939,7 +2942,7 @@
         <x:v>主负载：NVENC固定功能编码引擎、NVIDIA驱动、surface转换与内存拷贝；SDK/API提交线程通常只承担轻量调度。</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="78" customHeight="1">
+    <x:row r="36" ht="112" customHeight="1">
       <x:c r="A36" s="37" t="str">
         <x:v>SW-035</x:v>
       </x:c>
@@ -2959,7 +2962,7 @@
         <x:v>代理缓冲、超时、连接池和逐小包转发放大尾延迟</x:v>
       </x:c>
       <x:c r="G36" s="38" t="str">
-        <x:v>连接复用；流式buffer策略；请求/媒体大小限制；背压；慢客户端和重请求分流；可观测代理排队</x:v>
+        <x:v>① 构建AArch64优化的Envoy/Nginx发行版，TLS优先使用支持ARMv8 Crypto Extension的OpenSSL/BoringSSL实现；② 按NUMA部署worker、连接池和内存池，复用连接并隔离慢客户端与大媒体请求；③ 优化流式buffer、水位和批量write策略，减少逐token小包、系统调用和buffer copy；④ 将代理event loop、TLS、压缩、HTTP解析和Linux网络栈分别profile，NEON/SVE只用于真实数据面热点，不做形式化向量化。</x:v>
       </x:c>
       <x:c r="H36" s="38" t="str">
         <x:v>网关配置基线、压测矩阵、SLO告警</x:v>
@@ -3071,7 +3074,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad59a0594226439b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cff31ddae2c428f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3228,6 +3231,46 @@
         <x:v>优化项可以挂在上层责任田，但交付物必须指向主要真实负载库。后端可动态选择时，按生产配置分别归因，不得用调用库名称替代实际执行库。</x:v>
       </x:c>
     </x:row>
+    <x:row r="20" ht="86" customHeight="1">
+      <x:c r="A20" s="58" t="str">
+        <x:v>鲲鹏指令集口径</x:v>
+      </x:c>
+      <x:c r="B20" s="58" t="str">
+        <x:v>NEON作为鲲鹏AArch64基础SIMD路径；SVE/SVE2仅在目标机型实际支持时启用。软件应提供通用C/NEON/SVE多版本构建或运行时派发，禁止把SVE作为所有鲲鹏CPU的默认前提。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="86" customHeight="1">
+      <x:c r="A21" s="58" t="str">
+        <x:v>编译与发布口径</x:v>
+      </x:c>
+      <x:c r="B21" s="58" t="str">
+        <x:v>关键原生库建立鲲鹏目标构建，使用BiSheng/GCC/Clang针对实际CPU调优；对稳定热点评估O3、LTO、PGO和自动向量化报告，同时保留通用AArch64兼容包与回退。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="86" customHeight="1">
+      <x:c r="A22" s="58" t="str">
+        <x:v>NUMA与多核口径</x:v>
+      </x:c>
+      <x:c r="B22" s="58" t="str">
+        <x:v>鲲鹏多核场景统一线程预算、绑核、first-touch和NUMA本地内存；GPU/pinned memory/worker按PCIe根节点部署。所有SIMD优化必须同时验证内存带宽、cache miss和并发扩展效率。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="150" customHeight="1">
+      <x:c r="A23" s="58" t="str">
+        <x:v>JSON场景、库优先级与去重</x:v>
+      </x:c>
+      <x:c r="B23" s="58" t="str">
+        <x:v>SW-030保持一个统一需求并按场景验收。AI推理/Agent主支持：P0 Pydantic-core（含jiter）覆盖Schema解析、类型转换、Structured Output/tool_call校验及partial JSON；P0 orjson覆盖普通dict/list响应、SSE、metadata和日志序列化；P1 simdjson覆盖C/C++网关、大JSON和On-Demand；RapidJSON仅存量兼容，sonic-cpp待ARM成熟且有明确业务采用后条件支持。Pydantic-core与orjson仅在基础编解码上重叠：前者的独特价值是Schema与模型对象，后者是通用Python对象到bytes；jiter是Pydantic-core底层parser。带Schema输入优先model_validate_json，Pydantic模型输出优先model_dump_json，通用对象再使用orjson；禁止默认orjson.loads→Pydantic校验或model_dump→orjson.dumps的重复遍历。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="86" customHeight="1">
+      <x:c r="A24" s="58" t="str">
+        <x:v>鲲鹏/ARM资料</x:v>
+      </x:c>
+      <x:c r="B24" s="58" t="str">
+        <x:v>https://www.hikunpeng.com/document/detail/en/kunpengdevps/compilation/cm-bisheng/kunpengbisheng_30_0004.html ; https://www.hikunpeng.com/document/detail/en/kunpengdevps/userguide/cliuserguide/KunpengDevKitCli_0255.html ; https://developer.arm.com/community/arm-research/b/articles/posts/the-arm-scalable-vector-extension-sve</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
